--- a/validation_analysis/doe_track/TEST_SUMMARY.xlsx
+++ b/validation_analysis/doe_track/TEST_SUMMARY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\dissertation\validation_analysis\doe_track\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{06BEC79A-0DD1-40DE-9FCA-B85BA5F26E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95FD34E-C013-411F-A342-327D1E499932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="7"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -24,16 +24,16 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="20" r:id="rId9"/>
-    <pivotCache cacheId="115" r:id="rId10"/>
-    <pivotCache cacheId="127" r:id="rId11"/>
-    <pivotCache cacheId="142" r:id="rId12"/>
+    <pivotCache cacheId="0" r:id="rId9"/>
+    <pivotCache cacheId="1" r:id="rId10"/>
+    <pivotCache cacheId="2" r:id="rId11"/>
+    <pivotCache cacheId="3" r:id="rId12"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="49">
   <si>
     <t>Truck</t>
   </si>
@@ -143,12 +143,6 @@
     <t>Follow Gap Control</t>
   </si>
   <si>
-    <t>East Total</t>
-  </si>
-  <si>
-    <t>West Total</t>
-  </si>
-  <si>
     <t>PID</t>
   </si>
   <si>
@@ -191,7 +185,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -675,31 +669,20 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" pivotButton="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -745,7 +728,1639 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="286">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -844,7 +2459,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Evan Stegner" refreshedDate="45335.500150462962" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="139">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Evan Stegner" refreshedDate="45335.500150462962" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="139" xr:uid="{00000000-000A-0000-FFFF-FFFF14000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:E140" sheet="test_summary_DOE_track"/>
   </cacheSource>
@@ -909,7 +2524,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Evan Stegner" refreshedDate="45335.541645949073" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="30">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Evan Stegner" refreshedDate="45335.541645949073" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="30" xr:uid="{00000000-000A-0000-FFFF-FFFF73000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:E31" sheet="test_summary_jdsmc"/>
   </cacheSource>
@@ -960,7 +2575,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Evan Stegner" refreshedDate="45335.590833449074" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Evan Stegner" refreshedDate="45335.590833449074" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12" xr:uid="{00000000-000A-0000-FFFF-FFFF7F000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D13" sheet="test_summary_I85"/>
   </cacheSource>
@@ -999,7 +2614,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Evan Stegner" refreshedDate="45336.421393634257" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="15">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Evan Stegner" refreshedDate="45336.421393634257" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="15" xr:uid="{00000000-000A-0000-FFFF-FFFF8E000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:D16" sheet="test_summary_nrc"/>
   </cacheSource>
@@ -2408,7 +4023,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:F100" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -2783,35 +4398,35 @@
     <dataField name="Number of Replicates" fld="4" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="13">
+    <format dxfId="285">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
+    <format dxfId="284">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="283">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="282">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="281">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="280">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="279">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="278">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="277">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -2828,7 +4443,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
+    <format dxfId="276">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -2838,7 +4453,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="3">
+    <format dxfId="275">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -2848,7 +4463,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="2">
+    <format dxfId="274">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -2858,14 +4473,169 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="273">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="272">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000001000000}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0">
+  <location ref="A3:E13" firstHeaderRow="1" firstDataRow="2" firstDataCol="2"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" compact="0" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" compact="0" showAll="0">
+      <items count="5">
+        <item m="1" x="2"/>
+        <item m="1" x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Number of Replicates" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="13">
+    <format dxfId="33">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="32">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="31">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="30">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="29">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="28">
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="27">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+    </format>
+    <format dxfId="26">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="25">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="23">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="22">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -2881,103 +4651,11 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="127" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:D13" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="5">
-        <item m="1" x="2"/>
-        <item m="1" x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="0"/>
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="9">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Number of Replicates" fld="3" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="115" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:J14" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000002000000}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0">
+  <location ref="A3:F24" firstHeaderRow="1" firstDataRow="2" firstDataCol="3"/>
   <pivotFields count="5">
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" compact="0" showAll="0">
       <items count="7">
         <item m="1" x="4"/>
         <item m="1" x="5"/>
@@ -2988,14 +4666,14 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" compact="0" showAll="0">
       <items count="3">
         <item x="0"/>
         <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
+    <pivotField axis="axisRow" compact="0" showAll="0" defaultSubtotal="0">
       <items count="7">
         <item m="1" x="5"/>
         <item m="1" x="6"/>
@@ -3006,77 +4684,90 @@
         <item x="2"/>
       </items>
     </pivotField>
-    <pivotField axis="axisCol" showAll="0">
+    <pivotField axis="axisCol" compact="0" showAll="0">
       <items count="3">
         <item x="1"/>
         <item x="0"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" compact="0" showAll="0"/>
   </pivotFields>
-  <rowFields count="2">
+  <rowFields count="3">
     <field x="0"/>
     <field x="1"/>
+    <field x="2"/>
   </rowFields>
-  <rowItems count="9">
+  <rowItems count="20">
     <i>
       <x v="3"/>
     </i>
     <i r="1">
       <x/>
     </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
     <i>
       <x v="4"/>
     </i>
     <i r="1">
       <x/>
     </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="5"/>
+    </i>
+    <i r="2">
+      <x v="6"/>
+    </i>
     <i r="1">
       <x v="1"/>
     </i>
+    <i r="2">
+      <x v="5"/>
+    </i>
+    <i r="2">
+      <x v="6"/>
+    </i>
     <i>
       <x v="5"/>
     </i>
     <i r="1">
       <x/>
     </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="5"/>
+    </i>
+    <i r="2">
+      <x v="6"/>
+    </i>
     <i r="1">
       <x v="1"/>
     </i>
+    <i r="2">
+      <x v="5"/>
+    </i>
+    <i r="2">
+      <x v="6"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
-  <colFields count="2">
+  <colFields count="1">
     <field x="3"/>
-    <field x="2"/>
   </colFields>
-  <colItems count="9">
+  <colItems count="3">
     <i>
       <x/>
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i t="default">
-      <x/>
     </i>
     <i>
-      <x v="1"/>
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i t="default">
       <x v="1"/>
     </i>
     <i t="grand">
@@ -3086,6 +4777,157 @@
   <dataFields count="1">
     <dataField name="Number of Replicates" fld="4" baseField="0" baseItem="0"/>
   </dataFields>
+  <formats count="20">
+    <format dxfId="20">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="19">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="17">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="15">
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="11">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="1" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="9">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="2" count="2">
+            <x v="5"/>
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="4">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="3">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="3">
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="2" count="2">
+            <x v="5"/>
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="2">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -3099,17 +4941,17 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="142" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:B26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000003000000}" name="PivotTable4" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0">
+  <location ref="A3:J12" firstHeaderRow="1" firstDataRow="2" firstDataCol="2"/>
   <pivotFields count="4">
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" compact="0" showAll="0">
       <items count="3">
         <item x="0"/>
         <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" compact="0" showAll="0">
       <items count="6">
         <item x="1"/>
         <item m="1" x="3"/>
@@ -3119,7 +4961,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisCol" compact="0" showAll="0">
       <items count="8">
         <item x="2"/>
         <item x="3"/>
@@ -3131,90 +4973,75 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" compact="0" showAll="0"/>
   </pivotFields>
-  <rowFields count="3">
+  <rowFields count="2">
     <field x="0"/>
     <field x="1"/>
-    <field x="2"/>
   </rowFields>
-  <rowItems count="23">
+  <rowItems count="8">
     <i>
       <x/>
     </i>
     <i r="1">
       <x/>
     </i>
-    <i r="2">
-      <x v="6"/>
-    </i>
     <i r="1">
       <x v="3"/>
     </i>
-    <i r="2">
-      <x/>
-    </i>
-    <i r="2">
-      <x v="1"/>
-    </i>
-    <i r="2">
-      <x v="2"/>
-    </i>
-    <i r="2">
-      <x v="3"/>
-    </i>
-    <i r="2">
-      <x v="4"/>
-    </i>
-    <i r="2">
-      <x v="5"/>
-    </i>
     <i>
       <x v="1"/>
     </i>
     <i r="1">
       <x/>
     </i>
-    <i r="2">
-      <x v="6"/>
-    </i>
     <i r="1">
       <x v="3"/>
     </i>
-    <i r="2">
-      <x/>
-    </i>
-    <i r="2">
-      <x v="1"/>
-    </i>
-    <i r="2">
-      <x v="2"/>
-    </i>
-    <i r="2">
-      <x v="3"/>
-    </i>
-    <i r="2">
-      <x v="4"/>
-    </i>
-    <i r="2">
-      <x v="5"/>
-    </i>
     <i r="1">
       <x v="4"/>
     </i>
-    <i r="2">
-      <x v="3"/>
-    </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
-  <colItems count="1">
-    <i/>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
   </colItems>
   <dataFields count="1">
     <dataField name="Sum of GroupCount" fld="3" baseField="0" baseItem="0"/>
   </dataFields>
+  <formats count="1">
+    <format dxfId="0">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -3228,9 +5055,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3268,7 +5095,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3374,7 +5201,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3516,1637 +5343,1639 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A3:F100"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="6">
         <v>22</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="6">
         <v>29</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="6">
         <v>31</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="6">
         <v>47</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="6">
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="6">
         <v>4</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="6">
         <v>6</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="6">
         <v>7</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="6">
         <v>14</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="6">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="6">
         <v>7</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="6">
         <v>12</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="6">
         <v>11</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="6">
         <v>13</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="6">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <v>35</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9">
-        <v>3</v>
-      </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6">
+        <v>3</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <v>50</v>
       </c>
-      <c r="B9" s="9">
-        <v>3</v>
-      </c>
-      <c r="C9" s="9">
+      <c r="B9" s="6">
+        <v>3</v>
+      </c>
+      <c r="C9" s="6">
         <v>8</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="6">
         <v>5</v>
       </c>
-      <c r="E9" s="9">
-        <v>3</v>
-      </c>
-      <c r="F9" s="9">
+      <c r="E9" s="6">
+        <v>3</v>
+      </c>
+      <c r="F9" s="6">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <v>100</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="6">
         <v>4</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="6">
         <v>4</v>
       </c>
-      <c r="D10" s="9">
-        <v>3</v>
-      </c>
-      <c r="E10" s="9">
-        <v>3</v>
-      </c>
-      <c r="F10" s="9">
+      <c r="D10" s="6">
+        <v>3</v>
+      </c>
+      <c r="E10" s="6">
+        <v>3</v>
+      </c>
+      <c r="F10" s="6">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9">
-        <v>3</v>
-      </c>
-      <c r="F11" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6">
+        <v>3</v>
+      </c>
+      <c r="F11" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9">
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6">
         <v>4</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="6">
         <v>8</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="6">
         <v>9</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="6">
         <v>10</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="6">
         <v>12</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="6">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <v>35</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="6">
         <v>2</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9">
-        <v>3</v>
-      </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9">
+      <c r="C14" s="6"/>
+      <c r="D14" s="6">
+        <v>3</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="11">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <v>50</v>
       </c>
-      <c r="B15" s="9">
-        <v>3</v>
-      </c>
-      <c r="C15" s="9">
-        <v>3</v>
-      </c>
-      <c r="D15" s="9">
+      <c r="B15" s="6">
+        <v>3</v>
+      </c>
+      <c r="C15" s="6">
+        <v>3</v>
+      </c>
+      <c r="D15" s="6">
         <v>5</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9">
+      <c r="E15" s="6"/>
+      <c r="F15" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="11">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <v>100</v>
       </c>
-      <c r="B16" s="9">
-        <v>3</v>
-      </c>
-      <c r="C16" s="9">
+      <c r="B16" s="6">
+        <v>3</v>
+      </c>
+      <c r="C16" s="6">
         <v>6</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="6">
         <v>2</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9">
+      <c r="E16" s="6"/>
+      <c r="F16" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9">
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6">
         <v>6</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9">
-        <v>3</v>
-      </c>
-      <c r="F18" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6">
+        <v>3</v>
+      </c>
+      <c r="F18" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9">
-        <v>3</v>
-      </c>
-      <c r="F19" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6">
+        <v>3</v>
+      </c>
+      <c r="F19" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9">
+      <c r="B20" s="6"/>
+      <c r="C20" s="6">
         <v>2</v>
       </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9">
-        <v>3</v>
-      </c>
-      <c r="F20" s="9">
+      <c r="D20" s="6"/>
+      <c r="E20" s="6">
+        <v>3</v>
+      </c>
+      <c r="F20" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="11">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
         <v>100</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9">
+      <c r="B21" s="6"/>
+      <c r="C21" s="6">
         <v>2</v>
       </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9">
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9">
-        <v>3</v>
-      </c>
-      <c r="F22" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6">
+        <v>3</v>
+      </c>
+      <c r="F22" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9">
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6">
         <v>1</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="6">
         <v>2</v>
       </c>
-      <c r="F23" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="11">
+      <c r="F23" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <v>100</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9">
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6">
         <v>1</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="6">
         <v>2</v>
       </c>
-      <c r="F24" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
+      <c r="F24" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="9">
-        <v>3</v>
-      </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9">
+      <c r="B25" s="6">
+        <v>3</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6">
         <v>2</v>
       </c>
-      <c r="E25" s="9">
-        <v>3</v>
-      </c>
-      <c r="F25" s="9">
+      <c r="E25" s="6">
+        <v>3</v>
+      </c>
+      <c r="F25" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="11">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="5">
         <v>50</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="6">
         <v>2</v>
       </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9">
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="11">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="5">
         <v>100</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="6">
         <v>1</v>
       </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9">
+      <c r="C27" s="6"/>
+      <c r="D27" s="6">
         <v>2</v>
       </c>
-      <c r="E27" s="9">
-        <v>3</v>
-      </c>
-      <c r="F27" s="9">
+      <c r="E27" s="6">
+        <v>3</v>
+      </c>
+      <c r="F27" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="6">
         <v>22</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="6">
         <v>21</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="6">
         <v>28</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="6">
         <v>47</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="6">
         <v>118</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="6">
         <v>8</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="6">
         <v>4</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="6">
         <v>8</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="6">
         <v>17</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="6">
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9">
-        <v>3</v>
-      </c>
-      <c r="F30" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6">
+        <v>3</v>
+      </c>
+      <c r="F30" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="9">
-        <v>3</v>
-      </c>
-      <c r="C31" s="9">
+      <c r="B31" s="6">
+        <v>3</v>
+      </c>
+      <c r="C31" s="6">
         <v>7</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="6">
         <v>7</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="6">
         <v>7</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="6">
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="11">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="5">
         <v>35</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9">
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6">
         <v>2</v>
       </c>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9">
+      <c r="E32" s="6"/>
+      <c r="F32" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="11">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="5">
         <v>50</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33" s="6">
         <v>2</v>
       </c>
-      <c r="C33" s="9">
-        <v>3</v>
-      </c>
-      <c r="D33" s="9">
-        <v>3</v>
-      </c>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9">
+      <c r="C33" s="6">
+        <v>3</v>
+      </c>
+      <c r="D33" s="6">
+        <v>3</v>
+      </c>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="11">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="5">
         <v>100</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="6">
         <v>1</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="6">
         <v>4</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="6">
         <v>2</v>
       </c>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9">
+      <c r="E34" s="6"/>
+      <c r="F34" s="6">
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9">
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6">
         <v>4</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F35" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9">
-        <v>3</v>
-      </c>
-      <c r="F36" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6">
+        <v>3</v>
+      </c>
+      <c r="F36" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B37" s="9">
+      <c r="B37" s="6">
         <v>8</v>
       </c>
-      <c r="C37" s="9">
+      <c r="C37" s="6">
         <v>8</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="6">
         <v>10</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="6">
         <v>12</v>
       </c>
-      <c r="F37" s="9">
+      <c r="F37" s="6">
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="11">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="5">
         <v>35</v>
       </c>
-      <c r="B38" s="9">
+      <c r="B38" s="6">
         <v>2</v>
       </c>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9">
-        <v>3</v>
-      </c>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9">
+      <c r="C38" s="6"/>
+      <c r="D38" s="6">
+        <v>3</v>
+      </c>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="11">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="5">
         <v>50</v>
       </c>
-      <c r="B39" s="9">
-        <v>3</v>
-      </c>
-      <c r="C39" s="9">
+      <c r="B39" s="6">
+        <v>3</v>
+      </c>
+      <c r="C39" s="6">
         <v>2</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="6">
         <v>5</v>
       </c>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9">
+      <c r="E39" s="6"/>
+      <c r="F39" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="11">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="5">
         <v>100</v>
       </c>
-      <c r="B40" s="9">
-        <v>3</v>
-      </c>
-      <c r="C40" s="9">
+      <c r="B40" s="6">
+        <v>3</v>
+      </c>
+      <c r="C40" s="6">
         <v>6</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="6">
         <v>2</v>
       </c>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9">
+      <c r="E40" s="6"/>
+      <c r="F40" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="11" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9">
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6">
         <v>6</v>
       </c>
-      <c r="F41" s="9">
+      <c r="F41" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9">
-        <v>3</v>
-      </c>
-      <c r="F42" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="11" t="s">
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6">
+        <v>3</v>
+      </c>
+      <c r="F42" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9">
-        <v>3</v>
-      </c>
-      <c r="F43" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="10" t="s">
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6">
+        <v>3</v>
+      </c>
+      <c r="F43" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9">
+      <c r="B44" s="6"/>
+      <c r="C44" s="6">
         <v>2</v>
       </c>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9">
-        <v>3</v>
-      </c>
-      <c r="F44" s="9">
+      <c r="D44" s="6"/>
+      <c r="E44" s="6">
+        <v>3</v>
+      </c>
+      <c r="F44" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="11">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="5">
         <v>100</v>
       </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9">
+      <c r="B45" s="6"/>
+      <c r="C45" s="6">
         <v>2</v>
       </c>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9">
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="11" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9">
-        <v>3</v>
-      </c>
-      <c r="F46" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="10" t="s">
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6">
+        <v>3</v>
+      </c>
+      <c r="F46" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9">
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6">
         <v>1</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E47" s="6">
         <v>2</v>
       </c>
-      <c r="F47" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="11">
+      <c r="F47" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="5">
         <v>100</v>
       </c>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9">
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6">
         <v>1</v>
       </c>
-      <c r="E48" s="9">
+      <c r="E48" s="6">
         <v>2</v>
       </c>
-      <c r="F48" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="10" t="s">
+      <c r="F48" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B49" s="9">
-        <v>3</v>
-      </c>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9">
+      <c r="B49" s="6">
+        <v>3</v>
+      </c>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6">
         <v>2</v>
       </c>
-      <c r="E49" s="9">
-        <v>3</v>
-      </c>
-      <c r="F49" s="9">
+      <c r="E49" s="6">
+        <v>3</v>
+      </c>
+      <c r="F49" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="11">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="5">
         <v>50</v>
       </c>
-      <c r="B50" s="9">
+      <c r="B50" s="6">
         <v>2</v>
       </c>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9">
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="11">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="5">
         <v>100</v>
       </c>
-      <c r="B51" s="9">
+      <c r="B51" s="6">
         <v>1</v>
       </c>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9">
+      <c r="C51" s="6"/>
+      <c r="D51" s="6">
         <v>2</v>
       </c>
-      <c r="E51" s="9">
-        <v>3</v>
-      </c>
-      <c r="F51" s="9">
+      <c r="E51" s="6">
+        <v>3</v>
+      </c>
+      <c r="F51" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B52" s="9">
+      <c r="B52" s="6">
         <v>16</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="6">
         <v>23</v>
       </c>
-      <c r="D52" s="9">
+      <c r="D52" s="6">
         <v>24</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E52" s="6">
         <v>34</v>
       </c>
-      <c r="F52" s="9">
+      <c r="F52" s="6">
         <v>97</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="10" t="s">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B53" s="9">
+      <c r="B53" s="6">
         <v>2</v>
       </c>
-      <c r="C53" s="9">
+      <c r="C53" s="6">
         <v>4</v>
       </c>
-      <c r="D53" s="9">
+      <c r="D53" s="6">
         <v>6</v>
       </c>
-      <c r="E53" s="9">
+      <c r="E53" s="6">
         <v>7</v>
       </c>
-      <c r="F53" s="9">
+      <c r="F53" s="6">
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="10" t="s">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9">
-        <v>3</v>
-      </c>
-      <c r="F54" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="10" t="s">
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6">
+        <v>3</v>
+      </c>
+      <c r="F54" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B55" s="9">
-        <v>3</v>
-      </c>
-      <c r="C55" s="9">
+      <c r="B55" s="6">
+        <v>3</v>
+      </c>
+      <c r="C55" s="6">
         <v>8</v>
       </c>
-      <c r="D55" s="9">
+      <c r="D55" s="6">
         <v>6</v>
       </c>
-      <c r="E55" s="9">
+      <c r="E55" s="6">
         <v>5</v>
       </c>
-      <c r="F55" s="9">
+      <c r="F55" s="6">
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="11">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="5">
         <v>35</v>
       </c>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9">
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6">
         <v>2</v>
       </c>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9">
+      <c r="E56" s="6"/>
+      <c r="F56" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="11">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="5">
         <v>50</v>
       </c>
-      <c r="B57" s="9">
+      <c r="B57" s="6">
         <v>2</v>
       </c>
-      <c r="C57" s="9">
-        <v>3</v>
-      </c>
-      <c r="D57" s="9">
+      <c r="C57" s="6">
+        <v>3</v>
+      </c>
+      <c r="D57" s="6">
         <v>2</v>
       </c>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9">
+      <c r="E57" s="6"/>
+      <c r="F57" s="6">
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="11">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="5">
         <v>100</v>
       </c>
-      <c r="B58" s="9">
+      <c r="B58" s="6">
         <v>1</v>
       </c>
-      <c r="C58" s="9">
+      <c r="C58" s="6">
         <v>5</v>
       </c>
-      <c r="D58" s="9">
+      <c r="D58" s="6">
         <v>2</v>
       </c>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9">
+      <c r="E58" s="6"/>
+      <c r="F58" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="11" t="s">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9">
-        <v>3</v>
-      </c>
-      <c r="F59" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="11" t="s">
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6">
+        <v>3</v>
+      </c>
+      <c r="F59" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9">
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6">
         <v>2</v>
       </c>
-      <c r="F60" s="9">
+      <c r="F60" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="10" t="s">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B61" s="9">
+      <c r="B61" s="6">
         <v>8</v>
       </c>
-      <c r="C61" s="9">
+      <c r="C61" s="6">
         <v>9</v>
       </c>
-      <c r="D61" s="9">
+      <c r="D61" s="6">
         <v>9</v>
       </c>
-      <c r="E61" s="9">
+      <c r="E61" s="6">
         <v>11</v>
       </c>
-      <c r="F61" s="9">
+      <c r="F61" s="6">
         <v>37</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="11">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="5">
         <v>35</v>
       </c>
-      <c r="B62" s="9">
+      <c r="B62" s="6">
         <v>2</v>
       </c>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9">
-        <v>3</v>
-      </c>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9">
+      <c r="C62" s="6"/>
+      <c r="D62" s="6">
+        <v>3</v>
+      </c>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="11">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="5">
         <v>50</v>
       </c>
-      <c r="B63" s="9">
-        <v>3</v>
-      </c>
-      <c r="C63" s="9">
-        <v>3</v>
-      </c>
-      <c r="D63" s="9">
+      <c r="B63" s="6">
+        <v>3</v>
+      </c>
+      <c r="C63" s="6">
+        <v>3</v>
+      </c>
+      <c r="D63" s="6">
         <v>4</v>
       </c>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9">
+      <c r="E63" s="6"/>
+      <c r="F63" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="11">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="5">
         <v>100</v>
       </c>
-      <c r="B64" s="9">
-        <v>3</v>
-      </c>
-      <c r="C64" s="9">
+      <c r="B64" s="6">
+        <v>3</v>
+      </c>
+      <c r="C64" s="6">
         <v>6</v>
       </c>
-      <c r="D64" s="9">
+      <c r="D64" s="6">
         <v>2</v>
       </c>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9">
+      <c r="E64" s="6"/>
+      <c r="F64" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="11" t="s">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9">
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6">
         <v>6</v>
       </c>
-      <c r="F65" s="9">
+      <c r="F65" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="11" t="s">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9">
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6">
         <v>2</v>
       </c>
-      <c r="F66" s="9">
+      <c r="F66" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="11" t="s">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9">
-        <v>3</v>
-      </c>
-      <c r="F67" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="10" t="s">
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6">
+        <v>3</v>
+      </c>
+      <c r="F67" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9">
+      <c r="B68" s="6"/>
+      <c r="C68" s="6">
         <v>2</v>
       </c>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9">
-        <v>3</v>
-      </c>
-      <c r="F68" s="9">
+      <c r="D68" s="6"/>
+      <c r="E68" s="6">
+        <v>3</v>
+      </c>
+      <c r="F68" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="11">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="5">
         <v>100</v>
       </c>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9">
+      <c r="B69" s="6"/>
+      <c r="C69" s="6">
         <v>2</v>
       </c>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9">
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="11" t="s">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9">
-        <v>3</v>
-      </c>
-      <c r="F70" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="10" t="s">
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6">
+        <v>3</v>
+      </c>
+      <c r="F70" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9">
+      <c r="B71" s="6"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6">
         <v>1</v>
       </c>
-      <c r="E71" s="9">
+      <c r="E71" s="6">
         <v>2</v>
       </c>
-      <c r="F71" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="11">
+      <c r="F71" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="5">
         <v>100</v>
       </c>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9">
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6">
         <v>1</v>
       </c>
-      <c r="E72" s="9">
+      <c r="E72" s="6">
         <v>2</v>
       </c>
-      <c r="F72" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="10" t="s">
+      <c r="F72" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B73" s="9">
-        <v>3</v>
-      </c>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9">
+      <c r="B73" s="6">
+        <v>3</v>
+      </c>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6">
         <v>2</v>
       </c>
-      <c r="E73" s="9">
-        <v>3</v>
-      </c>
-      <c r="F73" s="9">
+      <c r="E73" s="6">
+        <v>3</v>
+      </c>
+      <c r="F73" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="11">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="5">
         <v>50</v>
       </c>
-      <c r="B74" s="9">
+      <c r="B74" s="6">
         <v>2</v>
       </c>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9">
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="11">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="5">
         <v>100</v>
       </c>
-      <c r="B75" s="9">
+      <c r="B75" s="6">
         <v>1</v>
       </c>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9">
+      <c r="C75" s="6"/>
+      <c r="D75" s="6">
         <v>2</v>
       </c>
-      <c r="E75" s="9">
-        <v>3</v>
-      </c>
-      <c r="F75" s="9">
+      <c r="E75" s="6">
+        <v>3</v>
+      </c>
+      <c r="F75" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="8" t="s">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B76" s="9">
+      <c r="B76" s="6">
         <v>22</v>
       </c>
-      <c r="C76" s="9">
+      <c r="C76" s="6">
         <v>31</v>
       </c>
-      <c r="D76" s="9">
+      <c r="D76" s="6">
         <v>31</v>
       </c>
-      <c r="E76" s="9">
+      <c r="E76" s="6">
         <v>41</v>
       </c>
-      <c r="F76" s="9">
+      <c r="F76" s="6">
         <v>125</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="10" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B77" s="9">
+      <c r="B77" s="6">
         <v>5</v>
       </c>
-      <c r="C77" s="9">
+      <c r="C77" s="6">
         <v>5</v>
       </c>
-      <c r="D77" s="9">
+      <c r="D77" s="6">
         <v>6</v>
       </c>
-      <c r="E77" s="9">
+      <c r="E77" s="6">
         <v>5</v>
       </c>
-      <c r="F77" s="9">
+      <c r="F77" s="6">
         <v>21</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="10" t="s">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9">
-        <v>3</v>
-      </c>
-      <c r="F78" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="10" t="s">
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6">
+        <v>3</v>
+      </c>
+      <c r="F78" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B79" s="9">
+      <c r="B79" s="6">
         <v>6</v>
       </c>
-      <c r="C79" s="9">
+      <c r="C79" s="6">
         <v>15</v>
       </c>
-      <c r="D79" s="9">
+      <c r="D79" s="6">
         <v>11</v>
       </c>
-      <c r="E79" s="9">
+      <c r="E79" s="6">
         <v>13</v>
       </c>
-      <c r="F79" s="9">
+      <c r="F79" s="6">
         <v>45</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="11">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="5">
         <v>35</v>
       </c>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9">
-        <v>3</v>
-      </c>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="11">
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6">
+        <v>3</v>
+      </c>
+      <c r="E80" s="6"/>
+      <c r="F80" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="5">
         <v>50</v>
       </c>
-      <c r="B81" s="9">
+      <c r="B81" s="6">
         <v>2</v>
       </c>
-      <c r="C81" s="9">
+      <c r="C81" s="6">
         <v>10</v>
       </c>
-      <c r="D81" s="9">
+      <c r="D81" s="6">
         <v>5</v>
       </c>
-      <c r="E81" s="9">
-        <v>3</v>
-      </c>
-      <c r="F81" s="9">
+      <c r="E81" s="6">
+        <v>3</v>
+      </c>
+      <c r="F81" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="11">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="5">
         <v>100</v>
       </c>
-      <c r="B82" s="9">
+      <c r="B82" s="6">
         <v>4</v>
       </c>
-      <c r="C82" s="9">
+      <c r="C82" s="6">
         <v>5</v>
       </c>
-      <c r="D82" s="9">
-        <v>3</v>
-      </c>
-      <c r="E82" s="9">
-        <v>3</v>
-      </c>
-      <c r="F82" s="9">
+      <c r="D82" s="6">
+        <v>3</v>
+      </c>
+      <c r="E82" s="6">
+        <v>3</v>
+      </c>
+      <c r="F82" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="11" t="s">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9">
-        <v>3</v>
-      </c>
-      <c r="F83" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="11" t="s">
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6">
+        <v>3</v>
+      </c>
+      <c r="F83" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B84" s="9"/>
-      <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="9">
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6">
         <v>4</v>
       </c>
-      <c r="F84" s="9">
+      <c r="F84" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="10" t="s">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B85" s="9">
+      <c r="B85" s="6">
         <v>8</v>
       </c>
-      <c r="C85" s="9">
+      <c r="C85" s="6">
         <v>9</v>
       </c>
-      <c r="D85" s="9">
+      <c r="D85" s="6">
         <v>11</v>
       </c>
-      <c r="E85" s="9">
+      <c r="E85" s="6">
         <v>12</v>
       </c>
-      <c r="F85" s="9">
+      <c r="F85" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="11">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="5">
         <v>35</v>
       </c>
-      <c r="B86" s="9">
+      <c r="B86" s="6">
         <v>2</v>
       </c>
-      <c r="C86" s="9"/>
-      <c r="D86" s="9">
-        <v>3</v>
-      </c>
-      <c r="E86" s="9"/>
-      <c r="F86" s="9">
+      <c r="C86" s="6"/>
+      <c r="D86" s="6">
+        <v>3</v>
+      </c>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="11">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="5">
         <v>50</v>
       </c>
-      <c r="B87" s="9">
-        <v>3</v>
-      </c>
-      <c r="C87" s="9">
-        <v>3</v>
-      </c>
-      <c r="D87" s="9">
+      <c r="B87" s="6">
+        <v>3</v>
+      </c>
+      <c r="C87" s="6">
+        <v>3</v>
+      </c>
+      <c r="D87" s="6">
         <v>5</v>
       </c>
-      <c r="E87" s="9"/>
-      <c r="F87" s="9">
+      <c r="E87" s="6"/>
+      <c r="F87" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="11">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="5">
         <v>100</v>
       </c>
-      <c r="B88" s="9">
-        <v>3</v>
-      </c>
-      <c r="C88" s="9">
+      <c r="B88" s="6">
+        <v>3</v>
+      </c>
+      <c r="C88" s="6">
         <v>6</v>
       </c>
-      <c r="D88" s="9">
-        <v>3</v>
-      </c>
-      <c r="E88" s="9"/>
-      <c r="F88" s="9">
+      <c r="D88" s="6">
+        <v>3</v>
+      </c>
+      <c r="E88" s="6"/>
+      <c r="F88" s="6">
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="11" t="s">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B89" s="9"/>
-      <c r="C89" s="9"/>
-      <c r="D89" s="9"/>
-      <c r="E89" s="9">
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="6">
         <v>6</v>
       </c>
-      <c r="F89" s="9">
+      <c r="F89" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="11" t="s">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9">
-        <v>3</v>
-      </c>
-      <c r="F90" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="11" t="s">
+      <c r="B90" s="6"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6">
+        <v>3</v>
+      </c>
+      <c r="F90" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B91" s="9"/>
-      <c r="C91" s="9"/>
-      <c r="D91" s="9"/>
-      <c r="E91" s="9">
-        <v>3</v>
-      </c>
-      <c r="F91" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="10" t="s">
+      <c r="B91" s="6"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6">
+        <v>3</v>
+      </c>
+      <c r="F91" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B92" s="9"/>
-      <c r="C92" s="9">
+      <c r="B92" s="6"/>
+      <c r="C92" s="6">
         <v>2</v>
       </c>
-      <c r="D92" s="9"/>
-      <c r="E92" s="9">
-        <v>3</v>
-      </c>
-      <c r="F92" s="9">
+      <c r="D92" s="6"/>
+      <c r="E92" s="6">
+        <v>3</v>
+      </c>
+      <c r="F92" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="11">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="5">
         <v>100</v>
       </c>
-      <c r="B93" s="9"/>
-      <c r="C93" s="9">
+      <c r="B93" s="6"/>
+      <c r="C93" s="6">
         <v>2</v>
       </c>
-      <c r="D93" s="9"/>
-      <c r="E93" s="9"/>
-      <c r="F93" s="9">
+      <c r="D93" s="6"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="11" t="s">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B94" s="9"/>
-      <c r="C94" s="9"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="9">
-        <v>3</v>
-      </c>
-      <c r="F94" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="10" t="s">
+      <c r="B94" s="6"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="6">
+        <v>3</v>
+      </c>
+      <c r="F94" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B95" s="9"/>
-      <c r="C95" s="9"/>
-      <c r="D95" s="9">
+      <c r="B95" s="6"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="6">
         <v>1</v>
       </c>
-      <c r="E95" s="9">
+      <c r="E95" s="6">
         <v>2</v>
       </c>
-      <c r="F95" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="11">
+      <c r="F95" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="5">
         <v>100</v>
       </c>
-      <c r="B96" s="9"/>
-      <c r="C96" s="9"/>
-      <c r="D96" s="9">
+      <c r="B96" s="6"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="6">
         <v>1</v>
       </c>
-      <c r="E96" s="9">
+      <c r="E96" s="6">
         <v>2</v>
       </c>
-      <c r="F96" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="10" t="s">
+      <c r="F96" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B97" s="9">
-        <v>3</v>
-      </c>
-      <c r="C97" s="9"/>
-      <c r="D97" s="9">
+      <c r="B97" s="6">
+        <v>3</v>
+      </c>
+      <c r="C97" s="6"/>
+      <c r="D97" s="6">
         <v>2</v>
       </c>
-      <c r="E97" s="9">
-        <v>3</v>
-      </c>
-      <c r="F97" s="9">
+      <c r="E97" s="6">
+        <v>3</v>
+      </c>
+      <c r="F97" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="11">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="5">
         <v>50</v>
       </c>
-      <c r="B98" s="9">
+      <c r="B98" s="6">
         <v>2</v>
       </c>
-      <c r="C98" s="9"/>
-      <c r="D98" s="9"/>
-      <c r="E98" s="9"/>
-      <c r="F98" s="9">
+      <c r="C98" s="6"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="11">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="5">
         <v>100</v>
       </c>
-      <c r="B99" s="9">
+      <c r="B99" s="6">
         <v>1</v>
       </c>
-      <c r="C99" s="9"/>
-      <c r="D99" s="9">
+      <c r="C99" s="6"/>
+      <c r="D99" s="6">
         <v>2</v>
       </c>
-      <c r="E99" s="9">
-        <v>3</v>
-      </c>
-      <c r="F99" s="9">
+      <c r="E99" s="6">
+        <v>3</v>
+      </c>
+      <c r="F99" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="8" t="s">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B100" s="9">
+      <c r="B100" s="6">
         <v>82</v>
       </c>
-      <c r="C100" s="9">
+      <c r="C100" s="6">
         <v>104</v>
       </c>
-      <c r="D100" s="9">
+      <c r="D100" s="6">
         <v>114</v>
       </c>
-      <c r="E100" s="9">
+      <c r="E100" s="6">
         <v>169</v>
       </c>
-      <c r="F100" s="9">
+      <c r="F100" s="6">
         <v>469</v>
       </c>
     </row>
@@ -5157,729 +6986,845 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A3:D13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A3:E13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="2"/>
+      <c r="C3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="2"/>
+      <c r="C5" s="6">
         <v>16</v>
       </c>
-      <c r="C5" s="5">
+      <c r="D5" s="6">
         <v>16</v>
       </c>
-      <c r="D5" s="5">
+      <c r="E5" s="6">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="5">
+      <c r="C6" s="6">
         <v>4</v>
       </c>
-      <c r="C6" s="5">
+      <c r="D6" s="6">
         <v>4</v>
       </c>
-      <c r="D6" s="5">
+      <c r="E6" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2">
         <v>75</v>
       </c>
-      <c r="B7" s="5">
+      <c r="C7" s="6">
         <v>7</v>
       </c>
-      <c r="C7" s="5">
+      <c r="D7" s="6">
         <v>7</v>
       </c>
-      <c r="D7" s="5">
+      <c r="E7" s="6">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2">
         <v>150</v>
       </c>
-      <c r="B8" s="5">
+      <c r="C8" s="6">
         <v>5</v>
       </c>
-      <c r="C8" s="5">
+      <c r="D8" s="6">
         <v>5</v>
       </c>
-      <c r="D8" s="5">
+      <c r="E8" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="2"/>
+      <c r="C9" s="6">
         <v>17</v>
       </c>
-      <c r="C9" s="5">
+      <c r="D9" s="6">
         <v>17</v>
       </c>
-      <c r="D9" s="5">
+      <c r="E9" s="6">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="5">
+      <c r="C10" s="6">
         <v>5</v>
       </c>
-      <c r="C10" s="5">
+      <c r="D10" s="6">
         <v>5</v>
       </c>
-      <c r="D10" s="5">
+      <c r="E10" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2">
         <v>75</v>
       </c>
-      <c r="B11" s="5">
+      <c r="C11" s="6">
         <v>7</v>
       </c>
-      <c r="C11" s="5">
+      <c r="D11" s="6">
         <v>7</v>
       </c>
-      <c r="D11" s="5">
+      <c r="E11" s="6">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2">
         <v>150</v>
       </c>
-      <c r="B12" s="5">
+      <c r="C12" s="6">
         <v>5</v>
       </c>
-      <c r="C12" s="5">
+      <c r="D12" s="6">
         <v>5</v>
       </c>
-      <c r="D12" s="5">
+      <c r="E12" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="2"/>
+      <c r="C13" s="6">
         <v>33</v>
       </c>
-      <c r="C13" s="5">
+      <c r="D13" s="6">
         <v>33</v>
       </c>
-      <c r="D13" s="5">
+      <c r="E13" s="6">
         <v>66</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A3:J14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A3:F24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="6">
+        <v>17</v>
+      </c>
+      <c r="E5" s="6">
+        <v>17</v>
+      </c>
+      <c r="F5" s="6">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="6">
+        <v>17</v>
+      </c>
+      <c r="E6" s="6">
+        <v>17</v>
+      </c>
+      <c r="F6" s="6">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="6">
+        <v>17</v>
+      </c>
+      <c r="E7" s="6">
+        <v>17</v>
+      </c>
+      <c r="F7" s="6">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="6">
+        <v>16</v>
+      </c>
+      <c r="E8" s="6">
+        <v>15</v>
+      </c>
+      <c r="F8" s="6">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="6">
+        <v>8</v>
+      </c>
+      <c r="E9" s="6">
+        <v>8</v>
+      </c>
+      <c r="F9" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="D11" s="6">
+        <v>4</v>
+      </c>
+      <c r="E11" s="6">
+        <v>4</v>
+      </c>
+      <c r="F11" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="6">
+        <v>3</v>
+      </c>
+      <c r="E12" s="6">
+        <v>3</v>
+      </c>
+      <c r="F12" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J4" t="s">
+      <c r="C13" s="2"/>
+      <c r="D13" s="6">
+        <v>8</v>
+      </c>
+      <c r="E13" s="6">
+        <v>7</v>
+      </c>
+      <c r="F13" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="6">
+        <v>2</v>
+      </c>
+      <c r="E14" s="6">
+        <v>2</v>
+      </c>
+      <c r="F14" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="6">
+        <v>6</v>
+      </c>
+      <c r="E15" s="6">
+        <v>5</v>
+      </c>
+      <c r="F15" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="6">
+        <v>15</v>
+      </c>
+      <c r="E16" s="6">
+        <v>14</v>
+      </c>
+      <c r="F16" s="6">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="6">
+        <v>7</v>
+      </c>
+      <c r="E17" s="6">
+        <v>7</v>
+      </c>
+      <c r="F17" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1</v>
+      </c>
+      <c r="F18" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="6">
+        <v>4</v>
+      </c>
+      <c r="E19" s="6">
+        <v>4</v>
+      </c>
+      <c r="F19" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="6">
+        <v>2</v>
+      </c>
+      <c r="E20" s="6">
+        <v>2</v>
+      </c>
+      <c r="F20" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="6">
+        <v>8</v>
+      </c>
+      <c r="E21" s="6">
+        <v>7</v>
+      </c>
+      <c r="F21" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="6">
+        <v>3</v>
+      </c>
+      <c r="E22" s="6">
+        <v>3</v>
+      </c>
+      <c r="F22" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="6">
+        <v>5</v>
+      </c>
+      <c r="E23" s="6">
+        <v>4</v>
+      </c>
+      <c r="F23" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="5">
-        <v>17</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5">
-        <v>17</v>
-      </c>
-      <c r="F6" s="5">
-        <v>17</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5">
-        <v>17</v>
-      </c>
-      <c r="J6" s="5">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="5">
-        <v>17</v>
-      </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5">
-        <v>17</v>
-      </c>
-      <c r="F7" s="5">
-        <v>17</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5">
-        <v>17</v>
-      </c>
-      <c r="J7" s="5">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="5">
-        <v>1</v>
-      </c>
-      <c r="C8" s="5">
-        <v>6</v>
-      </c>
-      <c r="D8" s="5">
-        <v>9</v>
-      </c>
-      <c r="E8" s="5">
-        <v>16</v>
-      </c>
-      <c r="F8" s="5">
-        <v>1</v>
-      </c>
-      <c r="G8" s="5">
-        <v>6</v>
-      </c>
-      <c r="H8" s="5">
-        <v>8</v>
-      </c>
-      <c r="I8" s="5">
-        <v>15</v>
-      </c>
-      <c r="J8" s="5">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="5">
-        <v>1</v>
-      </c>
-      <c r="C9" s="5">
-        <v>4</v>
-      </c>
-      <c r="D9" s="5">
-        <v>3</v>
-      </c>
-      <c r="E9" s="5">
-        <v>8</v>
-      </c>
-      <c r="F9" s="5">
-        <v>1</v>
-      </c>
-      <c r="G9" s="5">
-        <v>4</v>
-      </c>
-      <c r="H9" s="5">
-        <v>3</v>
-      </c>
-      <c r="I9" s="5">
-        <v>8</v>
-      </c>
-      <c r="J9" s="5">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5">
-        <v>2</v>
-      </c>
-      <c r="D10" s="5">
-        <v>6</v>
-      </c>
-      <c r="E10" s="5">
-        <v>8</v>
-      </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5">
-        <v>2</v>
-      </c>
-      <c r="H10" s="5">
-        <v>5</v>
-      </c>
-      <c r="I10" s="5">
-        <v>7</v>
-      </c>
-      <c r="J10" s="5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="5">
-        <v>1</v>
-      </c>
-      <c r="C11" s="5">
-        <v>7</v>
-      </c>
-      <c r="D11" s="5">
-        <v>7</v>
-      </c>
-      <c r="E11" s="5">
-        <v>15</v>
-      </c>
-      <c r="F11" s="5">
-        <v>1</v>
-      </c>
-      <c r="G11" s="5">
-        <v>7</v>
-      </c>
-      <c r="H11" s="5">
-        <v>6</v>
-      </c>
-      <c r="I11" s="5">
-        <v>14</v>
-      </c>
-      <c r="J11" s="5">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="5">
-        <v>1</v>
-      </c>
-      <c r="C12" s="5">
-        <v>4</v>
-      </c>
-      <c r="D12" s="5">
-        <v>2</v>
-      </c>
-      <c r="E12" s="5">
-        <v>7</v>
-      </c>
-      <c r="F12" s="5">
-        <v>1</v>
-      </c>
-      <c r="G12" s="5">
-        <v>4</v>
-      </c>
-      <c r="H12" s="5">
-        <v>2</v>
-      </c>
-      <c r="I12" s="5">
-        <v>7</v>
-      </c>
-      <c r="J12" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5">
-        <v>3</v>
-      </c>
-      <c r="D13" s="5">
-        <v>5</v>
-      </c>
-      <c r="E13" s="5">
-        <v>8</v>
-      </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5">
-        <v>3</v>
-      </c>
-      <c r="H13" s="5">
-        <v>4</v>
-      </c>
-      <c r="I13" s="5">
-        <v>7</v>
-      </c>
-      <c r="J13" s="5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="5">
-        <v>19</v>
-      </c>
-      <c r="C14" s="5">
-        <v>13</v>
-      </c>
-      <c r="D14" s="5">
-        <v>16</v>
-      </c>
-      <c r="E14" s="5">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="6">
         <v>48</v>
       </c>
-      <c r="F14" s="5">
-        <v>19</v>
-      </c>
-      <c r="G14" s="5">
-        <v>13</v>
-      </c>
-      <c r="H14" s="5">
-        <v>14</v>
-      </c>
-      <c r="I14" s="5">
+      <c r="E24" s="6">
         <v>46</v>
       </c>
-      <c r="J14" s="5">
+      <c r="F24" s="6">
         <v>94</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:B26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A3:J12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="3.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="2">
+        <v>30</v>
+      </c>
+      <c r="D4" s="2">
+        <v>40</v>
+      </c>
+      <c r="E4" s="2">
+        <v>50</v>
+      </c>
+      <c r="F4" s="2">
+        <v>75</v>
+      </c>
+      <c r="G4" s="2">
+        <v>150</v>
+      </c>
+      <c r="H4" s="2">
+        <v>258</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="6">
+        <v>3</v>
+      </c>
+      <c r="D5" s="6">
+        <v>4</v>
+      </c>
+      <c r="E5" s="6">
+        <v>3</v>
+      </c>
+      <c r="F5" s="6">
+        <v>3</v>
+      </c>
+      <c r="G5" s="6">
+        <v>1</v>
+      </c>
+      <c r="H5" s="6">
+        <v>3</v>
+      </c>
+      <c r="I5" s="6">
+        <v>6</v>
+      </c>
+      <c r="J5" s="6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6">
+        <v>6</v>
+      </c>
+      <c r="J6" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="6">
+        <v>3</v>
+      </c>
+      <c r="D7" s="6">
+        <v>4</v>
+      </c>
+      <c r="E7" s="6">
+        <v>3</v>
+      </c>
+      <c r="F7" s="6">
+        <v>3</v>
+      </c>
+      <c r="G7" s="6">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6">
+        <v>3</v>
+      </c>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6">
         <v>17</v>
       </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="5">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="6">
+        <v>3</v>
+      </c>
+      <c r="D8" s="6">
+        <v>4</v>
+      </c>
+      <c r="E8" s="6">
+        <v>3</v>
+      </c>
+      <c r="F8" s="6">
+        <v>4</v>
+      </c>
+      <c r="G8" s="6">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6">
+        <v>3</v>
+      </c>
+      <c r="I8" s="6">
+        <v>7</v>
+      </c>
+      <c r="J8" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="5">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6">
+        <v>7</v>
+      </c>
+      <c r="J9" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="6">
+        <v>3</v>
+      </c>
+      <c r="D10" s="6">
+        <v>4</v>
+      </c>
+      <c r="E10" s="6">
+        <v>3</v>
+      </c>
+      <c r="F10" s="6">
+        <v>3</v>
+      </c>
+      <c r="G10" s="6">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6">
+        <v>3</v>
+      </c>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6">
+        <v>1</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="6">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="5">
+      <c r="D12" s="6">
+        <v>8</v>
+      </c>
+      <c r="E12" s="6">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="5">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>30</v>
-      </c>
-      <c r="B8" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>40</v>
-      </c>
-      <c r="B9" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>50</v>
-      </c>
-      <c r="B10" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>75</v>
-      </c>
-      <c r="B11" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>150</v>
-      </c>
-      <c r="B12" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>258</v>
-      </c>
-      <c r="B13" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="5">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="5">
+      <c r="F12" s="6">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="5">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <v>30</v>
-      </c>
-      <c r="B18" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
-        <v>40</v>
-      </c>
-      <c r="B19" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
-        <v>50</v>
-      </c>
-      <c r="B20" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
-        <v>75</v>
-      </c>
-      <c r="B21" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
-        <v>150</v>
-      </c>
-      <c r="B22" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
-        <v>258</v>
-      </c>
-      <c r="B23" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
-        <v>75</v>
-      </c>
-      <c r="B25" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" s="5">
+      <c r="G12" s="6">
+        <v>2</v>
+      </c>
+      <c r="H12" s="6">
+        <v>6</v>
+      </c>
+      <c r="I12" s="6">
+        <v>13</v>
+      </c>
+      <c r="J12" s="6">
         <v>48</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5890,10 +7835,10 @@
         <v>29</v>
       </c>
       <c r="D1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -5907,7 +7852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -5921,7 +7866,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -5935,7 +7880,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -5949,7 +7894,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -5963,7 +7908,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -5977,7 +7922,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -5991,7 +7936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -6005,7 +7950,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -6019,7 +7964,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -6033,7 +7978,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -6047,7 +7992,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -6067,12 +8012,12 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6089,7 +8034,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -6106,7 +8051,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -6123,7 +8068,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -6140,7 +8085,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -6157,7 +8102,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6174,7 +8119,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -6191,7 +8136,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -6208,7 +8153,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -6225,7 +8170,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -6242,7 +8187,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -6259,7 +8204,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -6276,7 +8221,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -6293,7 +8238,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -6310,7 +8255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -6327,7 +8272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -6344,7 +8289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -6361,7 +8306,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -6378,7 +8323,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -6395,7 +8340,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -6412,7 +8357,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -6429,7 +8374,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -6446,7 +8391,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -6463,7 +8408,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -6480,7 +8425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -6497,7 +8442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -6514,7 +8459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -6531,7 +8476,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -6548,7 +8493,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -6565,7 +8510,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -6582,7 +8527,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -6599,7 +8544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -6616,7 +8561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -6633,7 +8578,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -6650,7 +8595,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -6667,7 +8612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -6684,7 +8629,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>14</v>
       </c>
@@ -6701,7 +8646,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -6718,7 +8663,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -6735,7 +8680,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>14</v>
       </c>
@@ -6752,7 +8697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>14</v>
       </c>
@@ -6769,7 +8714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>14</v>
       </c>
@@ -6786,7 +8731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>14</v>
       </c>
@@ -6803,7 +8748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>14</v>
       </c>
@@ -6820,7 +8765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>14</v>
       </c>
@@ -6837,7 +8782,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>14</v>
       </c>
@@ -6854,7 +8799,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>14</v>
       </c>
@@ -6871,7 +8816,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>14</v>
       </c>
@@ -6888,7 +8833,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>14</v>
       </c>
@@ -6905,7 +8850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>14</v>
       </c>
@@ -6922,7 +8867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>14</v>
       </c>
@@ -6939,7 +8884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>14</v>
       </c>
@@ -6956,7 +8901,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>14</v>
       </c>
@@ -6973,7 +8918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>14</v>
       </c>
@@ -6990,7 +8935,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>14</v>
       </c>
@@ -7007,7 +8952,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>14</v>
       </c>
@@ -7024,7 +8969,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>14</v>
       </c>
@@ -7041,7 +8986,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>14</v>
       </c>
@@ -7058,7 +9003,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>14</v>
       </c>
@@ -7075,7 +9020,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>14</v>
       </c>
@@ -7092,7 +9037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>14</v>
       </c>
@@ -7109,7 +9054,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>14</v>
       </c>
@@ -7126,7 +9071,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>14</v>
       </c>
@@ -7143,7 +9088,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>14</v>
       </c>
@@ -7160,7 +9105,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>14</v>
       </c>
@@ -7177,7 +9122,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>14</v>
       </c>
@@ -7194,7 +9139,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>14</v>
       </c>
@@ -7211,7 +9156,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>14</v>
       </c>
@@ -7228,7 +9173,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>14</v>
       </c>
@@ -7245,7 +9190,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>14</v>
       </c>
@@ -7262,7 +9207,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>15</v>
       </c>
@@ -7279,7 +9224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>15</v>
       </c>
@@ -7296,7 +9241,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>15</v>
       </c>
@@ -7313,7 +9258,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>15</v>
       </c>
@@ -7330,7 +9275,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>15</v>
       </c>
@@ -7347,7 +9292,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>15</v>
       </c>
@@ -7364,7 +9309,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>15</v>
       </c>
@@ -7381,7 +9326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>15</v>
       </c>
@@ -7398,7 +9343,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>15</v>
       </c>
@@ -7415,7 +9360,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>15</v>
       </c>
@@ -7432,7 +9377,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>15</v>
       </c>
@@ -7449,7 +9394,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>15</v>
       </c>
@@ -7466,7 +9411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>15</v>
       </c>
@@ -7483,7 +9428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>15</v>
       </c>
@@ -7500,7 +9445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>15</v>
       </c>
@@ -7517,7 +9462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>15</v>
       </c>
@@ -7534,7 +9479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>15</v>
       </c>
@@ -7551,7 +9496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>15</v>
       </c>
@@ -7568,7 +9513,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>15</v>
       </c>
@@ -7585,7 +9530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>15</v>
       </c>
@@ -7602,7 +9547,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>15</v>
       </c>
@@ -7619,7 +9564,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>15</v>
       </c>
@@ -7636,7 +9581,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>15</v>
       </c>
@@ -7653,7 +9598,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>15</v>
       </c>
@@ -7670,7 +9615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>15</v>
       </c>
@@ -7687,7 +9632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>15</v>
       </c>
@@ -7704,7 +9649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>15</v>
       </c>
@@ -7721,7 +9666,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>15</v>
       </c>
@@ -7738,7 +9683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>15</v>
       </c>
@@ -7755,7 +9700,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>15</v>
       </c>
@@ -7772,7 +9717,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>15</v>
       </c>
@@ -7789,7 +9734,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>15</v>
       </c>
@@ -7806,7 +9751,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>15</v>
       </c>
@@ -7823,7 +9768,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>15</v>
       </c>
@@ -7840,7 +9785,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>16</v>
       </c>
@@ -7857,7 +9802,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>16</v>
       </c>
@@ -7874,7 +9819,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>16</v>
       </c>
@@ -7891,7 +9836,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>16</v>
       </c>
@@ -7908,7 +9853,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>16</v>
       </c>
@@ -7925,7 +9870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>16</v>
       </c>
@@ -7942,7 +9887,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>16</v>
       </c>
@@ -7959,7 +9904,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>16</v>
       </c>
@@ -7976,7 +9921,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>16</v>
       </c>
@@ -7993,7 +9938,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>16</v>
       </c>
@@ -8010,7 +9955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>16</v>
       </c>
@@ -8027,7 +9972,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>16</v>
       </c>
@@ -8044,7 +9989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>16</v>
       </c>
@@ -8061,7 +10006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>16</v>
       </c>
@@ -8078,7 +10023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>16</v>
       </c>
@@ -8095,7 +10040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>16</v>
       </c>
@@ -8112,7 +10057,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>16</v>
       </c>
@@ -8129,7 +10074,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>16</v>
       </c>
@@ -8146,7 +10091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>16</v>
       </c>
@@ -8163,7 +10108,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>16</v>
       </c>
@@ -8180,7 +10125,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>16</v>
       </c>
@@ -8197,7 +10142,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>16</v>
       </c>
@@ -8214,7 +10159,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>16</v>
       </c>
@@ -8231,7 +10176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>16</v>
       </c>
@@ -8248,7 +10193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>16</v>
       </c>
@@ -8265,7 +10210,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>16</v>
       </c>
@@ -8282,7 +10227,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>16</v>
       </c>
@@ -8299,7 +10244,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>16</v>
       </c>
@@ -8316,7 +10261,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>16</v>
       </c>
@@ -8333,7 +10278,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>16</v>
       </c>
@@ -8350,7 +10295,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>16</v>
       </c>
@@ -8367,7 +10312,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>16</v>
       </c>
@@ -8384,7 +10329,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>16</v>
       </c>
@@ -8401,7 +10346,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>16</v>
       </c>
@@ -8418,7 +10363,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>16</v>
       </c>
@@ -8435,7 +10380,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>16</v>
       </c>
@@ -8458,17 +10403,17 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s">
         <v>35</v>
@@ -8477,18 +10422,18 @@
         <v>34</v>
       </c>
       <c r="E1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
         <v>31</v>
@@ -8497,15 +10442,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
         <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
         <v>30</v>
@@ -8514,15 +10459,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
         <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
         <v>31</v>
@@ -8531,15 +10476,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
         <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
         <v>30</v>
@@ -8548,15 +10493,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -8565,15 +10510,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
         <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
         <v>30</v>
@@ -8582,15 +10527,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
         <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
         <v>31</v>
@@ -8599,15 +10544,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
         <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
         <v>30</v>
@@ -8616,9 +10561,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
         <v>33</v>
@@ -8633,9 +10578,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
         <v>33</v>
@@ -8650,15 +10595,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
         <v>31</v>
@@ -8667,15 +10612,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
         <v>30</v>
@@ -8684,15 +10629,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
         <v>31</v>
@@ -8701,15 +10646,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
         <v>30</v>
@@ -8718,12 +10663,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
         <v>32</v>
@@ -8735,12 +10680,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
         <v>32</v>
@@ -8752,15 +10697,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s">
         <v>31</v>
@@ -8769,15 +10714,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B19" t="s">
         <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D19" t="s">
         <v>30</v>
@@ -8786,15 +10731,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
         <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
         <v>31</v>
@@ -8803,15 +10748,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
         <v>33</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
         <v>30</v>
@@ -8820,15 +10765,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B22" t="s">
         <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
         <v>31</v>
@@ -8837,15 +10782,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s">
         <v>30</v>
@@ -8854,9 +10799,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B24" t="s">
         <v>33</v>
@@ -8871,9 +10816,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
         <v>33</v>
@@ -8888,15 +10833,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s">
         <v>31</v>
@@ -8905,15 +10850,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D27" t="s">
         <v>30</v>
@@ -8922,15 +10867,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s">
         <v>31</v>
@@ -8939,15 +10884,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s">
         <v>30</v>
@@ -8956,12 +10901,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s">
         <v>32</v>
@@ -8973,12 +10918,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C31" t="s">
         <v>32</v>
@@ -8996,16 +10941,16 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
@@ -9014,12 +10959,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C2">
         <v>150</v>
@@ -9028,12 +10973,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>258</v>
@@ -9042,12 +10987,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C4">
         <v>30</v>
@@ -9056,12 +11001,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C5">
         <v>40</v>
@@ -9070,12 +11015,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C6">
         <v>50</v>
@@ -9084,12 +11029,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C7">
         <v>75</v>
@@ -9098,7 +11043,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -9112,12 +11057,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C9">
         <v>150</v>
@@ -9126,12 +11071,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C10">
         <v>258</v>
@@ -9140,12 +11085,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C11">
         <v>30</v>
@@ -9154,12 +11099,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C12">
         <v>40</v>
@@ -9168,12 +11113,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C13">
         <v>50</v>
@@ -9182,12 +11127,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C14">
         <v>75</v>
@@ -9196,7 +11141,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -9210,12 +11155,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C16">
         <v>75</v>
